--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>令和7年度。**ただし令和7年9月審査分に認定者数の断層がある**（961人→862人）。計上方法の確認を町に依頼中</t>
+          <t>令和7年度。**ただし令和7年9月審査分に認定者数の断層がある**（961人→862人）。計上方法の確認を町に依頼中。**第9期でも同じことが起きていた。**第9期の見込みは3か年の振れ幅が0.42％しかなく自然体推計そのものであり、その水準は令和5年度の実績より7.3％高い。実績／見込みが令和6年度98.6％・令和7年度91.1％となった理由がこれで説明できる。**見える化の令和8年度も月報の実績より8.0％高く、同じ幅である**（見込量算定の再検証 第2・3章）</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>バックテストで50設定を比較（推計方法のバックテスト・01_全設定）。保険料の月額まで通したケースはC1〜C6</t>
+          <t>バックテストで50設定を比較（推計方法のバックテスト・01_全設定）。保険料の月額まで通したケースはC1〜C6。**令和8年度の置き方は5通りを比べた。**月報の実績0.9598と、月報を使わない置き方（認定者数の伸び＋サービス別趨勢の半分）0.9694が1.0％差で揃う一方、現行方式1.0171はどちらからも離れる。**延ばし方を見える化の仕様にそろえた（9月25日）。**施設は利用者数一定、居住系・在宅は認定者数で延ばす。従前の置き方（第1号被保険者数で一律）との差は3年計6,678千円・月額13円</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>定員との突合（06）と必要利用定員総数（10）。認知症対応型共同生活介護は町内定員98人に対し利用は月43.8人で定員は制約として働いていない。**区域外利用は自給率67.57％でしか把握できず、事業所別の町内外利用は町に確認中（依頼票H15）**</t>
+          <t>定員との突合（06）と必要利用定員総数（10）。認知症対応型共同生活介護は町内定員98人に対し利用は月43.6人で定員は制約として働いていない。**区域外利用は自給率67.57％でしか把握できず、事業所別の町内外利用は町に確認中（依頼票H15）**</t>
         </is>
       </c>
     </row>
@@ -971,19 +971,73 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>依頼票（38項目＋確認事項14件）と据え置いた前提の一覧（09）。**本文に確認事項を書かず別の表で管理する形になっている**</t>
+          <t>依頼票（38項目＋確認事項14件）と据え置いた前提の一覧（09）。**本文に確認事項を書かず別の表で管理する形になっている。****厚生労働省の保険者別配布シート（標準の推計方法を当てはめた誤差。基本推計と包括推計の別）を依頼に追加した。**これがあれば推計手法の選択の妥当性を国のデータで確かめられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>付</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>論点の重みの基準</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>総給付費1％が保険料の月額で何円かを先に出す</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>**総給付費1％＝保険料の月額58.0円。**意思決定に効く論点と誤差の範囲の論点を分けるための基準。見える化の仕様との差13円は後者、令和8年度の置き方の差347円は前者にあたる</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>付</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>上限1.1・下限0.9</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>国のガイドの制約に収まるかを確かめる</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>**認定率・利用率・1人1月あたり回（日）数・1人1月あたり給付費の4項目とも適合。**最も振れるのはサービス利用率で1.00％</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>※ 判定　済＝この作業より前に済んでいる／今回＝令和8年9月24日の作業で埋めた／残＝資料の受領待ち／対象外＝小野町では生じない</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>**※ 今回埋めたのは第4・8・10・11・12・13段階の6つ。**</t>
         </is>
@@ -1450,13 +1504,13 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>3101160.491817961</v>
+        <v>3093948.167011783</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>6223.541950483398</v>
+        <v>6210.049325276944</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0</v>
@@ -1469,16 +1523,16 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>3207547.170923068</v>
+        <v>3200055.815611351</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.03430544126490576</v>
+        <v>0.03429522502377602</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>6422.567317019147</v>
+        <v>6408.552688972613</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>199.0253665357486</v>
+        <v>198.5033636956696</v>
       </c>
     </row>
     <row r="19">
@@ -1488,16 +1542,16 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>3195172.375427732</v>
+        <v>3187713.526282189</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.03031506555620389</v>
+        <v>0.03030605369222061</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>6399.416879107357</v>
+        <v>6385.463062730967</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>175.874928623959</v>
+        <v>175.4137374540232</v>
       </c>
     </row>
     <row r="20">
@@ -1507,16 +1561,16 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>3291279.767376745</v>
+        <v>3283568.127728037</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.06130584858809818</v>
+        <v>0.06128737473304025</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6579.212028935742</v>
+        <v>6564.785298817026</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>355.6700784523437</v>
+        <v>354.7359735400823</v>
       </c>
     </row>
     <row r="21">
@@ -1526,16 +1580,16 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>3132172.096736141</v>
+        <v>3124887.6486819</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>0.01000000000000001</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>6281.557635225326</v>
+        <v>6267.930083766808</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>58.01568474192754</v>
+        <v>57.88075848986409</v>
       </c>
     </row>
     <row r="22">
@@ -1545,16 +1599,16 @@
         </is>
       </c>
       <c r="B22" s="15" t="n">
-        <v>3147677.89919523</v>
+        <v>3140357.389516959</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>0.0149999999999999</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>6310.565477596288</v>
+        <v>6296.870463011738</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>87.0235271128895</v>
+        <v>86.82113773479432</v>
       </c>
     </row>
     <row r="24">
@@ -2370,7 +2424,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>総給付費2,876,614千円</t>
+          <t>総給付費2,869,936千円</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2474,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>標準給付費3,101,160千円</t>
+          <t>標準給付費3,093,948千円</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -735,44 +735,44 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>付</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>パターンの列挙</t>
+          <t>推計手法の妥当性</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>基準年度・出所・伸びの組合せを並べる</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>済</t>
+          <t>基本推計と包括推計のどちらが当たるかを確かめる</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>バックテストで50設定を比較（推計方法のバックテスト・01_全設定）。保険料の月額まで通したケースはC1〜C6。**令和8年度の置き方は5通りを比べた。**月報の実績0.9598と、月報を使わない置き方（認定者数の伸び＋サービス別趨勢の半分）0.9694が1.0％差で揃う一方、現行方式1.0171はどちらからも離れる。**延ばし方を見える化の仕様にそろえた（9月25日）。**施設は利用者数一定、居住系・在宅は認定者数で延ばす。従前の置き方（第1号被保険者数で一律）との差は3年計6,678千円・月額13円</t>
+          <t>**国のデータ（見える化「推計パターン毎の乖離状況」）で検証した。**認定者数の誤差は令和6年度▲3.10％・令和7年度＋3.23％（基本推計）で、全国1,267位・1,015位／約1,570保険者と中位より下。**サービス別では誤差10％超が10件あり、標準の推計方法は小野町では当たらない。**当方が実績を基点として総額を月報で裏づけていることの裏づけになる</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>伸びの置き方</t>
+          <t>パターンの列挙</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正するかを決める</t>
+          <t>基準年度・出所・伸びの組合せを並べる</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -782,105 +782,105 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>**補正（φ0.5・上限±3％）は総給付費の誤差5.39％で一律5.28％に劣る。**手引きの判定基準により採らない。採用は利用率・第1号被保険者数・窓3年（3.31％）</t>
+          <t>バックテストで50設定を比較（推計方法のバックテスト・01_全設定）。保険料の月額まで通したケースはC1〜C6。**令和8年度の置き方は5通りを比べた。**月報の実績0.9598と、月報を使わない置き方（認定者数の伸び＋サービス別趨勢の半分）0.9694が1.0％差で揃う一方、現行方式1.0171はどちらからも離れる。**延ばし方を見える化の仕様にそろえた（9月25日）。**施設は利用者数一定、居住系・在宅は認定者数で延ばす。従前の置き方（第1号被保険者数で一律）との差は3年計6,678千円・月額13円</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>季節性</t>
+          <t>伸びの置き方</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>基準年度が完結年度なら補正しない</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>今回</t>
+          <t>対計画比の偏りを補正するかを決める</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>**基準年度が令和7年度（完結年度）であるため季節補正は恒等的に不要。**念のため月報28か月で測ったところ、居宅は再現せず、地域密着型は再現せず、施設は再現、受給者計は再現。再現する2区分も差は2％前後で向きが逆であり、合計では相殺される</t>
+          <t>**補正（φ0.5・上限±3％）は総給付費の誤差5.39％で一律5.28％に劣る。**手引きの判定基準により採らない。採用は利用率・第1号被保険者数・窓3年（3.31％）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>供給実現性</t>
+          <t>季節性</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>需要量と供給可能量を分けて示す</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>済</t>
+          <t>基準年度が完結年度なら補正しない</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>定員との突合（06）と必要利用定員総数（10）。認知症対応型共同生活介護は町内定員98人に対し利用は月43.6人で定員は制約として働いていない。**区域外利用は自給率67.57％でしか把握できず、事業所別の町内外利用は町に確認中（依頼票H15）**</t>
+          <t>**基準年度が令和7年度（完結年度）であるため季節補正は恒等的に不要。**念のため月報28か月で測ったところ、居宅は再現せず、地域密着型は再現せず、施設は再現、受給者計は再現。再現する2区分も差は2％前後で向きが逆であり、合計では相殺される</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>施策反映</t>
+          <t>供給実現性</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>算定式に変数があるものだけを反映する</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>今回</t>
+          <t>需要量と供給可能量を分けて示す</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>**当方の式で変数になっているのは第1号被保険者数だけで、利用率・1人当たりの量・単価は基準年度で固定されている。**成果指標40件のうち目標値が確定しているものは0件（すべて協議会で設定）。**したがって現時点で見込量に反映できる施策はない。**歯止めを先に定めた（シート03）</t>
+          <t>定員との突合（06）と必要利用定員総数（10）。認知症対応型共同生活介護は町内定員98人に対し利用は月43.6人で定員は制約として働いていない。**区域外利用は自給率67.57％でしか把握できず、事業所別の町内外利用は町に確認中（依頼票H15）**</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>趨勢外の要因</t>
+          <t>施策反映</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>測れるもの・向きのみ・測れないものに分ける</t>
+          <t>算定式に変数があるものだけを反映する</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -890,24 +890,24 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>**単価は改定のない年でも年率+1.09％伸びており、改定のあった年（+1.25％）と差がない。**当方は単価を固定しているため、実績の趨勢（年率+1.13％）で置くと標準給付費が+3.43％、保険料が月額+199円上がる。令和9年度の報酬改定率＋1％の効きは月額+58円</t>
+          <t>**当方の式で変数になっているのは第1号被保険者数だけで、利用率・1人当たりの量・単価は基準年度で固定されている。**成果指標40件のうち目標値が確定しているものは0件（すべて協議会で設定）。**したがって現時点で見込量に反映できる施策はない。**歯止めを先に定めた（シート03）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>記載事項の点検</t>
+          <t>趨勢外の要因</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>法・基本指針の記載事項と突き合わせる</t>
+          <t>測れるもの・向きのみ・測れないものに分ける</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -917,24 +917,24 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>**介護保険法117条2項1号の必要利用定員総数（9月16日に追加）と同項2号の地域支援事業の量の見込み（今回追加）が落ちていた。**いずれも努力義務ではなく必須記載事項。量のうち13事業は町の事業実績待ち。認知症基本法13条の要請は9月16日に点検済み</t>
+          <t>**単価は改定のない年でも年率+1.09％伸びており、改定のあった年（+1.25％）と差がない。**当方は単価を固定しているため、実績の趨勢（年率+1.13％）で置くと標準給付費が+3.43％、保険料が月額+199円上がる。令和9年度の報酬改定率＋1％の効きは月額+58円</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>自己点検</t>
+          <t>記載事項の点検</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>点検を算定に組み込み、不適合なら異常終了する</t>
+          <t>法・基本指針の記載事項と突き合わせる</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -944,61 +944,61 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>**selfcheck() を設け、1件でも不適合なら AssertionError で止まる形にした（シート05）。**12項目</t>
+          <t>**介護保険法117条2項1号の必要利用定員総数（9月16日に追加）と同項2号の地域支援事業の量の見込み（今回追加）が落ちていた。**いずれも努力義務ではなく必須記載事項。量のうち13事業は町の事業実績待ち。認知症基本法13条の要請は9月16日に点検済み</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>確認事項の整理</t>
+          <t>自己点検</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>確定していない事項を一覧にする</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>済</t>
+          <t>点検を算定に組み込み、不適合なら異常終了する</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>依頼票（38項目＋確認事項14件）と据え置いた前提の一覧（09）。**本文に確認事項を書かず別の表で管理する形になっている。****厚生労働省の保険者別配布シート（標準の推計方法を当てはめた誤差。基本推計と包括推計の別）を依頼に追加した。**これがあれば推計手法の選択の妥当性を国のデータで確かめられる</t>
+          <t>**selfcheck() を設け、1件でも不適合なら AssertionError で止まる形にした（シート05）。**12項目</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>付</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>論点の重みの基準</t>
+          <t>確認事項の整理</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>総給付費1％が保険料の月額で何円かを先に出す</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>今回</t>
+          <t>確定していない事項を一覧にする</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>**総給付費1％＝保険料の月額58.0円。**意思決定に効く論点と誤差の範囲の論点を分けるための基準。見える化の仕様との差13円は後者、令和8年度の置き方の差347円は前者にあたる</t>
+          <t>依頼票（38項目＋確認事項14件）と据え置いた前提の一覧（09）。**本文に確認事項を書かず別の表で管理する形になっている。****9月25日に、見える化システムの「推計パターン毎の乖離状況」から推計手法の妥当性を検証した（推計手法の妥当性検証）。**基本推計と包括推計の優劣は年度で逆転し、2年平均では基本推計がわずかに優る。現行の設定を変える理由はない</t>
         </is>
       </c>
     </row>
@@ -1010,34 +1010,61 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
+          <t>論点の重みの基準</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>総給付費1％が保険料の月額で何円かを先に出す</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>**総給付費1％＝保険料の月額58.0円。**意思決定に効く論点と誤差の範囲の論点を分けるための基準。見える化の仕様との差13円は後者、令和8年度の置き方の差347円は前者にあたる</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>付</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>上限1.1・下限0.9</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>国のガイドの制約に収まるかを確かめる</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>今回</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>**認定率・利用率・1人1月あたり回（日）数・1人1月あたり給付費の4項目とも適合。**最も振れるのはサービス利用率で1.00％</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>※ 判定　済＝この作業より前に済んでいる／今回＝令和8年9月24日の作業で埋めた／残＝資料の受領待ち／対象外＝小野町では生じない</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>※ 判定　済＝この作業より前に済んでいる／今回＝令和8年9月24日の作業で埋めた／残＝資料の受領待ち／対象外＝小野町では生じない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>**※ 今回埋めたのは第4・8・10・11・12・13段階の6つ。**</t>
         </is>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>**単価は改定のない年でも年率+1.09％伸びており、改定のあった年（+1.25％）と差がない。**当方は単価を固定しているため、実績の趨勢（年率+1.13％）で置くと標準給付費が+3.43％、保険料が月額+199円上がる。令和9年度の報酬改定率＋1％の効きは月額+58円</t>
+          <t>**単価は改定のない年でも年率+1.09％伸びており、改定のあった年（+1.25％）と差がない。**当方は単価を固定しているため、実績の趨勢（年率+1.13％）で置くと標準給付費が+3.43％、保険料が月額+195円上がる。令和9年度の報酬改定率＋1％の効きは月額+57円</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>6210.049325276944</v>
+        <v>6094.769932174226</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>0.03429522502377602</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>6408.552688972613</v>
+        <v>6289.951382822092</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>198.5033636956696</v>
+        <v>195.1814506478668</v>
       </c>
     </row>
     <row r="19">
@@ -1575,10 +1575,10 @@
         <v>0.03030605369222061</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>6385.463062730967</v>
+        <v>6267.248156736358</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>175.4137374540232</v>
+        <v>172.4782245621327</v>
       </c>
     </row>
     <row r="20">
@@ -1594,10 +1594,10 @@
         <v>0.06128737473304025</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6564.785298817026</v>
+        <v>6443.569472008156</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>354.7359735400823</v>
+        <v>348.7995398339308</v>
       </c>
     </row>
     <row r="21">
@@ -1613,10 +1613,10 @@
         <v>0.01000000000000001</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>6267.930083766808</v>
+        <v>6151.682068051029</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>57.88075848986409</v>
+        <v>56.9121358768034</v>
       </c>
     </row>
     <row r="22">
@@ -1632,10 +1632,10 @@
         <v>0.0149999999999999</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>6296.870463011738</v>
+        <v>6180.138135989429</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>86.82113773479432</v>
+        <v>85.36820381520374</v>
       </c>
     </row>
     <row r="24">
@@ -1648,7 +1648,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>**※ 当方は単価を令和7年度で固定している。**実績の趨勢（年率+1.13％）で置くと保険料は月額+199円上がる。**固定は安全側ではなく過小側の置き方である。**</t>
+          <t>**※ 当方は単価を令和7年度で固定している。**実績の趨勢（年率+1.13％）で置くと保険料は月額+195円上がる。**固定は安全側ではなく過小側の置き方である。**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>6094.769932174226</v>
+        <v>6047.770970556241</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0.03429522502377602</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>6289.951382822092</v>
+        <v>6242.952421204108</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>195.1814506478668</v>
@@ -1575,7 +1575,7 @@
         <v>0.03030605369222061</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>6267.248156736358</v>
+        <v>6220.249195118374</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>172.4782245621327</v>
@@ -1594,10 +1594,10 @@
         <v>0.06128737473304025</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6443.569472008156</v>
+        <v>6396.570510390168</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>348.7995398339308</v>
+        <v>348.7995398339272</v>
       </c>
     </row>
     <row r="21">
@@ -1613,7 +1613,7 @@
         <v>0.01000000000000001</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>6151.682068051029</v>
+        <v>6104.683106433044</v>
       </c>
       <c r="E21" s="17" t="n">
         <v>56.9121358768034</v>
@@ -1632,10 +1632,10 @@
         <v>0.0149999999999999</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>6180.138135989429</v>
+        <v>6133.139174371444</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>85.36820381520374</v>
+        <v>85.36820381520283</v>
       </c>
     </row>
     <row r="24">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>要介護度別に分解する（川崎町方式。断層の解消が前提）</t>
+          <t>要介護度別に分解する（他町村の案件①方式。断層の解消が前提）</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>**令和7年9月の断層の原因が確認できるまで、認定者数を基礎とする方法は採れない。**川崎町方式（要介護度別）が使えるかもここにかかる</t>
+          <t>**令和7年9月の断層の原因が確認できるまで、認定者数を基礎とする方法は採れない。**他町村の案件①方式（要介護度別）が使えるかもここにかかる</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_見込量算定の手引き適合点検_20260925.xlsx
@@ -2098,7 +2098,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>**年率＋1.13％。固定していることで月額211円の過小になりうる**</t>
+          <t>**年率＋1.13％。固定していることで月額195円の過小になりうる**</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>12,000千円で月額▲103円、35,000千円で月額▲300円</t>
+          <t>取崩額に比例し、35,000千円で月額▲300円。残高は令和8年度末見込210,000千円</t>
         </is>
       </c>
     </row>
